--- a/10-06-2026.xlsx
+++ b/10-06-2026.xlsx
@@ -106,7 +106,7 @@
     <t>2º</t>
   </si>
   <si>
-    <t>536</t>
+    <t>537</t>
   </si>
   <si>
     <t>1.640</t>
@@ -115,7 +115,7 @@
     <t>1.718</t>
   </si>
   <si>
-    <t>3.185</t>
+    <t>3.190</t>
   </si>
   <si>
     <t>Atendimentos com CPF (com e sem compra)</t>
@@ -127,7 +127,7 @@
     <t>451</t>
   </si>
   <si>
-    <t>513</t>
+    <t>514</t>
   </si>
   <si>
     <t>1.563</t>
@@ -136,7 +136,7 @@
     <t>1.635</t>
   </si>
   <si>
-    <t>3.043</t>
+    <t>3.048</t>
   </si>
   <si>
     <t>Atendimentos Uso Indevido</t>
@@ -178,22 +178,22 @@
     <t>65º</t>
   </si>
   <si>
-    <t>117,20%</t>
+    <t>117,16%</t>
   </si>
   <si>
     <t>4º</t>
   </si>
   <si>
-    <t>127,78%</t>
-  </si>
-  <si>
-    <t>128,33%</t>
+    <t>127,77%</t>
+  </si>
+  <si>
+    <t>128,31%</t>
   </si>
   <si>
     <t>10º</t>
   </si>
   <si>
-    <t>126,26%</t>
+    <t>126,24%</t>
   </si>
   <si>
     <t>% Atendimentos Uso Indevido</t>
@@ -256,10 +256,10 @@
     <t>6º</t>
   </si>
   <si>
-    <t>00:13:12</t>
-  </si>
-  <si>
-    <t>00:13:34</t>
+    <t>00:13:13</t>
+  </si>
+  <si>
+    <t>00:13:35</t>
   </si>
   <si>
     <t>13º</t>
@@ -289,13 +289,13 @@
     <t>1.378</t>
   </si>
   <si>
-    <t>2.731</t>
+    <t>2.737</t>
   </si>
   <si>
     <t>Boletos ID</t>
   </si>
   <si>
-    <t>3.149</t>
+    <t>3.151</t>
   </si>
   <si>
     <t>351</t>
@@ -310,18 +310,15 @@
     <t>1.177</t>
   </si>
   <si>
-    <t>1.218</t>
-  </si>
-  <si>
-    <t>2.403</t>
+    <t>1.219</t>
+  </si>
+  <si>
+    <t>2.409</t>
   </si>
   <si>
     <t>Boletos ID Cliente Uso Indevido</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -331,7 +328,7 @@
     <t>Boletos ID Cliente TMA CPF Abaixo de 2min</t>
   </si>
   <si>
-    <t>657</t>
+    <t>658</t>
   </si>
   <si>
     <t>57</t>
@@ -349,52 +346,52 @@
     <t>231</t>
   </si>
   <si>
-    <t>486</t>
+    <t>487</t>
   </si>
   <si>
     <t>% Boletos ID Cliente Válidos (IAF)</t>
   </si>
   <si>
-    <t>90,58%</t>
+    <t>90,61%</t>
   </si>
   <si>
     <t>21º</t>
   </si>
   <si>
-    <t>92,13%</t>
+    <t>92,17%</t>
   </si>
   <si>
     <t>20º</t>
   </si>
   <si>
-    <t>92,29%</t>
-  </si>
-  <si>
-    <t>238º</t>
-  </si>
-  <si>
-    <t>91,37%</t>
-  </si>
-  <si>
-    <t>90,50%</t>
+    <t>92,33%</t>
+  </si>
+  <si>
+    <t>240º</t>
+  </si>
+  <si>
+    <t>91,40%</t>
+  </si>
+  <si>
+    <t>90,51%</t>
   </si>
   <si>
     <t>3º</t>
   </si>
   <si>
-    <t>89,14%</t>
+    <t>89,15%</t>
   </si>
   <si>
     <t>18º</t>
   </si>
   <si>
-    <t>91,30%</t>
+    <t>91,33%</t>
   </si>
   <si>
     <t>% Boletos ID Cliente Uso Indevido</t>
   </si>
   <si>
-    <t>0,41%</t>
+    <t>0,44%</t>
   </si>
   <si>
     <t>0,36%</t>
@@ -403,13 +400,16 @@
     <t>0,32%</t>
   </si>
   <si>
-    <t>147º</t>
-  </si>
-  <si>
-    <t>0,39%</t>
-  </si>
-  <si>
-    <t>0,45%</t>
+    <t>143º</t>
+  </si>
+  <si>
+    <t>0,42%</t>
+  </si>
+  <si>
+    <t>0,40%</t>
+  </si>
+  <si>
+    <t>0,46%</t>
   </si>
   <si>
     <t>14º</t>
@@ -418,19 +418,19 @@
     <t>% Boleto ID Cliente TMA CPF Abaixo de 2min</t>
   </si>
   <si>
-    <t>20,86%</t>
-  </si>
-  <si>
-    <t>11,12%</t>
-  </si>
-  <si>
-    <t>11,89%</t>
-  </si>
-  <si>
-    <t>107º</t>
-  </si>
-  <si>
-    <t>16,73%</t>
+    <t>20,88%</t>
+  </si>
+  <si>
+    <t>11,16%</t>
+  </si>
+  <si>
+    <t>11,93%</t>
+  </si>
+  <si>
+    <t>106º</t>
+  </si>
+  <si>
+    <t>16,75%</t>
   </si>
   <si>
     <t>13,12%</t>
@@ -439,7 +439,7 @@
     <t>15,24%</t>
   </si>
   <si>
-    <t>16,97%</t>
+    <t>17,00%</t>
   </si>
   <si>
     <t>ATENDIMENTOS NO ID CLIENTE</t>
@@ -787,6 +787,9 @@
     <t>00:05:17</t>
   </si>
   <si>
+    <t>00:02:52</t>
+  </si>
+  <si>
     <t>00:04:15</t>
   </si>
   <si>
@@ -1261,7 +1264,7 @@
     <t>Camila Reis Nascimento</t>
   </si>
   <si>
-    <t>00:02:46</t>
+    <t>00:02:40</t>
   </si>
   <si>
     <t>Carla Nunes Rosa Fernandes</t>
@@ -1906,12 +1909,12 @@
     <t>Maria Aline Ferreira Alves</t>
   </si>
   <si>
+    <t>00:40:48</t>
+  </si>
+  <si>
     <t>01:03:05</t>
   </si>
   <si>
-    <t>00:40:48</t>
-  </si>
-  <si>
     <t>Maria Andreza Silva De Oliveira</t>
   </si>
   <si>
@@ -2233,12 +2236,12 @@
     <t>Samara Alves Gomes</t>
   </si>
   <si>
+    <t>01:00:40</t>
+  </si>
+  <si>
     <t>00:09:57</t>
   </si>
   <si>
-    <t>01:00:40</t>
-  </si>
-  <si>
     <t>Samara Dayane Do Nascimento Alves De Morais</t>
   </si>
   <si>
@@ -2282,9 +2285,6 @@
   </si>
   <si>
     <t>Suziane Da Silva Lima Araujo</t>
-  </si>
-  <si>
-    <t>00:02:40</t>
   </si>
   <si>
     <t>Suzy Nascimento Pessoa De Luna</t>
@@ -3356,31 +3356,31 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>29</v>
@@ -3397,116 +3397,116 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>55</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>55</v>
@@ -3535,7 +3535,7 @@
         <v>134</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>135</v>
@@ -10459,16 +10459,16 @@
         <v>89</v>
       </c>
       <c r="X57" s="5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y57" s="6">
-        <v>-0.3371</v>
+        <v>-0.3258</v>
       </c>
       <c r="Z57" s="5">
         <v>0</v>
       </c>
       <c r="AA57" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB57" s="6">
         <v>0</v>
@@ -10495,19 +10495,19 @@
         <v>0</v>
       </c>
       <c r="AJ57" s="6">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="AK57" s="6">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="AL57" s="6">
         <v>0.2809</v>
       </c>
       <c r="AM57" s="6">
-        <v>0.35590000000000005</v>
+        <v>0.35</v>
       </c>
       <c r="AN57" s="6">
-        <v>0.075</v>
+        <v>0.0691</v>
       </c>
     </row>
     <row r="58" spans="1:40" x14ac:dyDescent="0.25">
@@ -10807,10 +10807,10 @@
         <v>256</v>
       </c>
       <c r="R60" s="7" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="S60" s="6">
-        <v>-0.4428</v>
+        <v>-0.4575</v>
       </c>
       <c r="T60" s="5">
         <v>57</v>
@@ -10825,10 +10825,10 @@
         <v>51</v>
       </c>
       <c r="X60" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y60" s="6">
-        <v>-0.451</v>
+        <v>-0.4314</v>
       </c>
       <c r="Z60" s="5">
         <v>0</v>
@@ -10843,19 +10843,19 @@
         <v>16</v>
       </c>
       <c r="AD60" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE60" s="6">
-        <v>-0.5</v>
+        <v>-0.4375</v>
       </c>
       <c r="AF60" s="6">
         <v>0.8946999999999999</v>
       </c>
       <c r="AG60" s="6">
-        <v>0.9333</v>
+        <v>0.9667</v>
       </c>
       <c r="AH60" s="6">
-        <v>0.038599999999999995</v>
+        <v>0.0719</v>
       </c>
       <c r="AI60" s="6">
         <v>0</v>
@@ -10870,10 +10870,10 @@
         <v>0.31370000000000003</v>
       </c>
       <c r="AM60" s="6">
-        <v>0.2857</v>
+        <v>0.3103</v>
       </c>
       <c r="AN60" s="6">
-        <v>-0.027999999999999997</v>
+        <v>-0.0034000000000000002</v>
       </c>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.25">
@@ -10926,10 +10926,10 @@
         <v>0.0046</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R61" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S61" s="6">
         <v>0.056799999999999996</v>
@@ -11048,10 +11048,10 @@
         <v>0</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R62" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="S62" s="6">
         <v>-0.3298</v>
@@ -11173,7 +11173,7 @@
         <v>211</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S63" s="6">
         <v>0.2625</v>
@@ -11295,7 +11295,7 @@
         <v>238</v>
       </c>
       <c r="R64" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S64" s="6">
         <v>-0.052300000000000006</v>
@@ -11414,7 +11414,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R65" s="7" t="s">
         <v>161</v>
@@ -11536,10 +11536,10 @@
         <v>0.0455</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R66" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S66" s="6">
         <v>-0.3833</v>
@@ -11658,7 +11658,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R67" s="7" t="s">
         <v>256</v>
@@ -11780,10 +11780,10 @@
         <v>-0.018600000000000002</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R68" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S68" s="6">
         <v>-0.3892</v>
@@ -11905,7 +11905,7 @@
         <v>254</v>
       </c>
       <c r="R69" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S69" s="6">
         <v>0.48109999999999997</v>
@@ -12024,10 +12024,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R70" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="S70" s="6">
         <v>-0.018799999999999997</v>
@@ -12146,10 +12146,10 @@
         <v>0</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R71" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S71" s="6">
         <v>-0.24780000000000002</v>
@@ -12268,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R72" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="S72" s="6">
         <v>-0.3023</v>
@@ -12390,10 +12390,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R73" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S73" s="6">
         <v>1.9480000000000002</v>
@@ -12515,7 +12515,7 @@
         <v>233</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="S74" s="6">
         <v>-0.091</v>
@@ -12634,10 +12634,10 @@
         <v>-0.0101</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="S75" s="6">
         <v>-0.2243</v>
@@ -12759,7 +12759,7 @@
         <v>233</v>
       </c>
       <c r="R76" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="S76" s="6">
         <v>0.6201</v>
@@ -12878,10 +12878,10 @@
         <v>-0.0167</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R77" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S77" s="6">
         <v>-0.1375</v>
@@ -13000,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>256</v>
@@ -13122,10 +13122,10 @@
         <v>0</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="R79" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S79" s="6">
         <v>-0.4045</v>
@@ -13247,7 +13247,7 @@
         <v>78</v>
       </c>
       <c r="R80" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S80" s="6">
         <v>-0.4889</v>
@@ -13366,10 +13366,10 @@
         <v>0.013300000000000001</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R81" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="S81" s="6">
         <v>0.0613</v>
@@ -13491,7 +13491,7 @@
         <v>256</v>
       </c>
       <c r="R82" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S82" s="6">
         <v>0.7634000000000001</v>
@@ -13732,10 +13732,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R84" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S84" s="6">
         <v>-0.1674</v>
@@ -13854,10 +13854,10 @@
         <v>-0.0308</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R85" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="S85" s="6">
         <v>0.276</v>
@@ -13976,10 +13976,10 @@
         <v>0</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R86" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S86" s="6">
         <v>1.2144</v>
@@ -14098,10 +14098,10 @@
         <v>0</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R87" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="S87" s="6">
         <v>-0.25730000000000003</v>
@@ -14223,7 +14223,7 @@
         <v>180</v>
       </c>
       <c r="R88" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S88" s="6">
         <v>-0.043</v>
@@ -14342,10 +14342,10 @@
         <v>0</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R89" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="S89" s="6">
         <v>0.5719</v>
@@ -14467,7 +14467,7 @@
         <v>243</v>
       </c>
       <c r="R90" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S90" s="6">
         <v>0.2079</v>
@@ -14586,10 +14586,10 @@
         <v>0.1176</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R91" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S91" s="6">
         <v>1.9696</v>
@@ -14708,10 +14708,10 @@
         <v>0</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R92" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="S92" s="6">
         <v>0.1934</v>
@@ -14830,10 +14830,10 @@
         <v>0</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R93" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="S93" s="6">
         <v>-0.43479999999999996</v>
@@ -14952,10 +14952,10 @@
         <v>0</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R94" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S94" s="6">
         <v>2.0385</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R95" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S95" s="6">
         <v>-0.2732</v>
@@ -15196,10 +15196,10 @@
         <v>0</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R96" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="S96" s="6">
         <v>3.5112</v>
@@ -15318,10 +15318,10 @@
         <v>0</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S97" s="6">
         <v>1.4469</v>
@@ -15440,10 +15440,10 @@
         <v>-0.057699999999999994</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S98" s="6">
         <v>-0.18510000000000001</v>
@@ -15562,7 +15562,7 @@
         <v>0.04650000000000001</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>158</v>
@@ -15684,7 +15684,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R100" s="7" t="s">
         <v>243</v>
@@ -15806,10 +15806,10 @@
         <v>0</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R101" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="S101" s="6">
         <v>-0.166</v>
@@ -15928,10 +15928,10 @@
         <v>0.0263</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="R102" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S102" s="6">
         <v>0.3822</v>
@@ -16050,10 +16050,10 @@
         <v>0</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R103" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S103" s="6">
         <v>0.3285</v>
@@ -16172,10 +16172,10 @@
         <v>0</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R104" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="S104" s="6">
         <v>-0.0184</v>
@@ -16297,7 +16297,7 @@
         <v>172</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S105" s="6">
         <v>1.1429</v>
@@ -16416,10 +16416,10 @@
         <v>0</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R106" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S106" s="6">
         <v>0.7637</v>
@@ -16538,10 +16538,10 @@
         <v>0</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R107" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S107" s="6">
         <v>0.6186</v>
@@ -16660,10 +16660,10 @@
         <v>0</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S108" s="6">
         <v>0</v>
@@ -16785,7 +16785,7 @@
         <v>185</v>
       </c>
       <c r="R109" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S109" s="6">
         <v>-0.23379999999999998</v>
@@ -17020,7 +17020,7 @@
         <v>10</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>142</v>
@@ -17047,7 +17047,7 @@
         <v>150</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>152</v>
@@ -17056,7 +17056,7 @@
         <v>153</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -17064,7 +17064,7 @@
         <v>21364</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C2" s="13">
         <v>17</v>
@@ -17079,7 +17079,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H2" s="13">
         <v>13</v>
@@ -17108,7 +17108,7 @@
         <v>21432</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C3" s="13">
         <v>15</v>
@@ -17123,7 +17123,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H3" s="13">
         <v>12</v>
@@ -17152,7 +17152,7 @@
         <v>21417</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C4" s="13">
         <v>18</v>
@@ -17167,7 +17167,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H4" s="13">
         <v>16</v>
@@ -17176,19 +17176,19 @@
         <v>15</v>
       </c>
       <c r="J4" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="14">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="M4" s="14">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="N4" s="14">
-        <v>0.6667000000000001</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -17196,7 +17196,7 @@
         <v>12175</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C5" s="13">
         <v>36</v>
@@ -17211,7 +17211,7 @@
         <v>0.0833</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H5" s="13">
         <v>17</v>
@@ -17240,7 +17240,7 @@
         <v>21427</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C6" s="13">
         <v>30</v>
@@ -17255,7 +17255,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H6" s="13">
         <v>12</v>
@@ -17284,7 +17284,7 @@
         <v>21415</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C7" s="13">
         <v>26</v>
@@ -17299,7 +17299,7 @@
         <v>0.0385</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H7" s="13">
         <v>12</v>
@@ -17328,7 +17328,7 @@
         <v>21424</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C8" s="13">
         <v>20</v>
@@ -17343,7 +17343,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H8" s="13">
         <v>20</v>
@@ -17372,7 +17372,7 @@
         <v>24599</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C9" s="13">
         <v>8</v>
@@ -17387,7 +17387,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H9" s="13">
         <v>10</v>
@@ -17416,7 +17416,7 @@
         <v>21411</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C10" s="13">
         <v>11</v>
@@ -17431,7 +17431,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H10" s="13">
         <v>9</v>
@@ -17460,7 +17460,7 @@
         <v>12643</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C11" s="13">
         <v>3</v>
@@ -17504,7 +17504,7 @@
         <v>19598</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C12" s="13">
         <v>12</v>
@@ -17519,7 +17519,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H12" s="13">
         <v>8</v>
@@ -17548,7 +17548,7 @@
         <v>11992</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C13" s="13">
         <v>16</v>
@@ -17563,7 +17563,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H13" s="13">
         <v>15</v>
@@ -17592,7 +17592,7 @@
         <v>21432</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C14" s="13">
         <v>20</v>
@@ -17607,7 +17607,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H14" s="13">
         <v>5</v>
@@ -17636,7 +17636,7 @@
         <v>19602</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C15" s="13">
         <v>5</v>
@@ -17651,7 +17651,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H15" s="13">
         <v>6</v>
@@ -17680,7 +17680,7 @@
         <v>21750</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C16" s="13">
         <v>21</v>
@@ -17695,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H16" s="13">
         <v>18</v>
@@ -17724,7 +17724,7 @@
         <v>7427</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C17" s="13">
         <v>10</v>
@@ -17739,7 +17739,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H17" s="13">
         <v>7</v>
@@ -17768,7 +17768,7 @@
         <v>21764</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C18" s="13">
         <v>15</v>
@@ -17783,7 +17783,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H18" s="13">
         <v>17</v>
@@ -17812,7 +17812,7 @@
         <v>23258</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C19" s="13">
         <v>11</v>
@@ -17827,7 +17827,7 @@
         <v>0.2727</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H19" s="13">
         <v>8</v>
@@ -17856,7 +17856,7 @@
         <v>21026</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C20" s="13">
         <v>13</v>
@@ -17871,7 +17871,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H20" s="13">
         <v>12</v>
@@ -17900,7 +17900,7 @@
         <v>21559</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C21" s="13">
         <v>12</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H21" s="13">
         <v>11</v>
@@ -17944,7 +17944,7 @@
         <v>21421</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C22" s="13">
         <v>44</v>
@@ -17959,7 +17959,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H22" s="13">
         <v>18</v>
@@ -17988,7 +17988,7 @@
         <v>22054</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C23" s="13">
         <v>8</v>
@@ -18003,7 +18003,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H23" s="13">
         <v>6</v>
@@ -18032,7 +18032,7 @@
         <v>21424</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C24" s="13">
         <v>26</v>
@@ -18076,7 +18076,7 @@
         <v>20931</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C25" s="13">
         <v>17</v>
@@ -18091,7 +18091,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H25" s="13">
         <v>10</v>
@@ -18120,7 +18120,7 @@
         <v>21428</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C26" s="13">
         <v>25</v>
@@ -18135,7 +18135,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H26" s="13">
         <v>19</v>
@@ -18164,7 +18164,7 @@
         <v>19598</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C27" s="13">
         <v>9</v>
@@ -18179,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H27" s="13">
         <v>8</v>
@@ -18208,7 +18208,7 @@
         <v>21761</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C28" s="13">
         <v>6</v>
@@ -18223,7 +18223,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H28" s="13">
         <v>7</v>
@@ -18252,7 +18252,7 @@
         <v>21418</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C29" s="13">
         <v>27</v>
@@ -18267,7 +18267,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H29" s="13">
         <v>17</v>
@@ -18296,7 +18296,7 @@
         <v>21422</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C30" s="13">
         <v>0</v>
@@ -18311,7 +18311,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H30" s="13">
         <v>1</v>
@@ -18340,7 +18340,7 @@
         <v>7432</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C31" s="13">
         <v>12</v>
@@ -18355,7 +18355,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H31" s="13">
         <v>10</v>
@@ -18384,7 +18384,7 @@
         <v>20856</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C32" s="13">
         <v>16</v>
@@ -18399,7 +18399,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H32" s="13">
         <v>12</v>
@@ -18428,7 +18428,7 @@
         <v>20763</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C33" s="13">
         <v>21</v>
@@ -18472,7 +18472,7 @@
         <v>21426</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C34" s="13">
         <v>14</v>
@@ -18487,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H34" s="13">
         <v>13</v>
@@ -18516,7 +18516,7 @@
         <v>11591</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C35" s="13">
         <v>34</v>
@@ -18560,7 +18560,7 @@
         <v>23776</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C36" s="13">
         <v>0</v>
@@ -18575,7 +18575,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H36" s="13">
         <v>2</v>
@@ -18604,7 +18604,7 @@
         <v>24598</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C37" s="13">
         <v>12</v>
@@ -18619,7 +18619,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H37" s="13">
         <v>9</v>
@@ -18648,7 +18648,7 @@
         <v>19601</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C38" s="13">
         <v>6</v>
@@ -18692,7 +18692,7 @@
         <v>14329</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C39" s="13">
         <v>13</v>
@@ -18707,7 +18707,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H39" s="13">
         <v>9</v>
@@ -18736,7 +18736,7 @@
         <v>23779</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C40" s="13">
         <v>5</v>
@@ -18751,7 +18751,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H40" s="13">
         <v>4</v>
@@ -18780,7 +18780,7 @@
         <v>23474</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C41" s="13">
         <v>10</v>
@@ -18795,7 +18795,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H41" s="13">
         <v>11</v>
@@ -18824,7 +18824,7 @@
         <v>14329</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C42" s="13">
         <v>13</v>
@@ -18868,7 +18868,7 @@
         <v>21428</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C43" s="13">
         <v>27</v>
@@ -18883,7 +18883,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H43" s="13">
         <v>24</v>
@@ -18912,7 +18912,7 @@
         <v>21270</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C44" s="13">
         <v>9</v>
@@ -18927,7 +18927,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H44" s="13">
         <v>8</v>
@@ -18956,7 +18956,7 @@
         <v>21416</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C45" s="13">
         <v>13</v>
@@ -18971,7 +18971,7 @@
         <v>0.0833</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H45" s="13">
         <v>12</v>
@@ -19000,7 +19000,7 @@
         <v>21420</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C46" s="13">
         <v>20</v>
@@ -19015,7 +19015,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H46" s="13">
         <v>10</v>
@@ -19041,90 +19041,90 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>7427</v>
+        <v>21122</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C47" s="13">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D47" s="13">
         <v>0</v>
       </c>
       <c r="E47" s="14">
-        <v>1.1667</v>
+        <v>3</v>
       </c>
       <c r="F47" s="14">
         <v>0</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>408</v>
+        <v>330</v>
       </c>
       <c r="H47" s="13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I47" s="13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J47" s="13">
         <v>0</v>
       </c>
       <c r="K47" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="14">
-        <v>0.9167000000000001</v>
+        <v>0</v>
       </c>
       <c r="M47" s="14">
         <v>0</v>
       </c>
       <c r="N47" s="14">
-        <v>0.0909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>21122</v>
+        <v>7427</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C48" s="13">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D48" s="13">
         <v>0</v>
       </c>
       <c r="E48" s="14">
-        <v>3</v>
+        <v>1.1667</v>
       </c>
       <c r="F48" s="14">
         <v>0</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>329</v>
+        <v>409</v>
       </c>
       <c r="H48" s="13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I48" s="13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J48" s="13">
         <v>0</v>
       </c>
       <c r="K48" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="14">
-        <v>0</v>
+        <v>0.9167000000000001</v>
       </c>
       <c r="M48" s="14">
         <v>0</v>
       </c>
       <c r="N48" s="14">
-        <v>0</v>
+        <v>0.0909</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -19132,7 +19132,7 @@
         <v>21431</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C49" s="13">
         <v>21</v>
@@ -19147,7 +19147,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H49" s="13">
         <v>21</v>
@@ -19176,7 +19176,7 @@
         <v>20934</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C50" s="13">
         <v>27</v>
@@ -19191,7 +19191,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H50" s="13">
         <v>13</v>
@@ -19220,7 +19220,7 @@
         <v>23717</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C51" s="13">
         <v>12</v>
@@ -19235,7 +19235,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H51" s="13">
         <v>11</v>
@@ -19264,7 +19264,7 @@
         <v>21420</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C52" s="13">
         <v>34</v>
@@ -19279,28 +19279,28 @@
         <v>0</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H52" s="13">
         <v>20</v>
       </c>
       <c r="I52" s="13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J52" s="13">
         <v>0</v>
       </c>
       <c r="K52" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L52" s="14">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="M52" s="14">
         <v>0</v>
       </c>
       <c r="N52" s="14">
-        <v>0.2778</v>
+        <v>0.31579999999999997</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -19308,7 +19308,7 @@
         <v>21412</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C53" s="13">
         <v>6</v>
@@ -19323,7 +19323,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H53" s="13">
         <v>6</v>
@@ -19352,7 +19352,7 @@
         <v>21429</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C54" s="13">
         <v>16</v>
@@ -19367,7 +19367,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H54" s="13">
         <v>20</v>
@@ -19396,7 +19396,7 @@
         <v>21417</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C55" s="13">
         <v>18</v>
@@ -19411,7 +19411,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H55" s="13">
         <v>17</v>
@@ -19440,7 +19440,7 @@
         <v>23773</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C56" s="13">
         <v>1</v>
@@ -19455,7 +19455,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H56" s="13">
         <v>1</v>
@@ -19484,7 +19484,7 @@
         <v>21424</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C57" s="13">
         <v>19</v>
@@ -19499,7 +19499,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H57" s="13">
         <v>17</v>
@@ -19528,7 +19528,7 @@
         <v>21764</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C58" s="13">
         <v>22</v>
@@ -19572,7 +19572,7 @@
         <v>21427</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C59" s="13">
         <v>34</v>
@@ -19587,7 +19587,7 @@
         <v>0.0909</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H59" s="13">
         <v>16</v>
@@ -19616,7 +19616,7 @@
         <v>23258</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="13">
         <v>11</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H60" s="13">
         <v>8</v>
@@ -19660,7 +19660,7 @@
         <v>21430</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C61" s="13">
         <v>18</v>
@@ -19704,7 +19704,7 @@
         <v>21766</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C62" s="13">
         <v>21</v>
@@ -19719,7 +19719,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H62" s="13">
         <v>18</v>
@@ -19748,7 +19748,7 @@
         <v>21270</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C63" s="13">
         <v>11</v>
@@ -19763,7 +19763,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H63" s="13">
         <v>7</v>
@@ -19792,7 +19792,7 @@
         <v>19599</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C64" s="13">
         <v>12</v>
@@ -19836,7 +19836,7 @@
         <v>7957</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C65" s="13">
         <v>13</v>
@@ -19880,7 +19880,7 @@
         <v>21426</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C66" s="13">
         <v>12</v>
@@ -19895,7 +19895,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H66" s="13">
         <v>12</v>
@@ -19924,7 +19924,7 @@
         <v>21417</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C67" s="13">
         <v>22</v>
@@ -19939,7 +19939,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H67" s="13">
         <v>11</v>
@@ -19968,7 +19968,7 @@
         <v>21763</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C68" s="13">
         <v>0</v>
@@ -19983,7 +19983,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H68" s="13">
         <v>5</v>
@@ -20012,7 +20012,7 @@
         <v>21422</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C69" s="13">
         <v>35</v>
@@ -20056,7 +20056,7 @@
         <v>21417</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C70" s="13">
         <v>7</v>
@@ -20071,7 +20071,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H70" s="13">
         <v>9</v>
@@ -20100,7 +20100,7 @@
         <v>24594</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C71" s="13">
         <v>14</v>
@@ -20115,7 +20115,7 @@
         <v>0.0833</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H71" s="13">
         <v>10</v>
@@ -20144,7 +20144,7 @@
         <v>19595</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C72" s="13">
         <v>16</v>
@@ -20188,7 +20188,7 @@
         <v>20923</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C73" s="13">
         <v>22</v>
@@ -20232,7 +20232,7 @@
         <v>21365</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C74" s="13">
         <v>17</v>
@@ -20247,7 +20247,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H74" s="13">
         <v>5</v>
@@ -20276,7 +20276,7 @@
         <v>21417</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C75" s="13">
         <v>15</v>
@@ -20291,7 +20291,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H75" s="13">
         <v>13</v>
@@ -20320,7 +20320,7 @@
         <v>20924</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C76" s="13">
         <v>34</v>
@@ -20364,7 +20364,7 @@
         <v>24594</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C77" s="13">
         <v>11</v>
@@ -20379,7 +20379,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H77" s="13">
         <v>10</v>
@@ -20408,7 +20408,7 @@
         <v>19595</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C78" s="13">
         <v>20</v>
@@ -20423,7 +20423,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H78" s="13">
         <v>16</v>
@@ -20452,7 +20452,7 @@
         <v>19601</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C79" s="13">
         <v>0</v>
@@ -20467,7 +20467,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H79" s="13">
         <v>1</v>
@@ -20496,7 +20496,7 @@
         <v>7424</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C80" s="13">
         <v>4</v>
@@ -20511,7 +20511,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H80" s="13">
         <v>4</v>
@@ -20540,7 +20540,7 @@
         <v>23473</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C81" s="13">
         <v>3</v>
@@ -20555,7 +20555,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H81" s="13">
         <v>3</v>
@@ -20584,7 +20584,7 @@
         <v>12517</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C82" s="13">
         <v>7</v>
@@ -20628,7 +20628,7 @@
         <v>24598</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C83" s="13">
         <v>0</v>
@@ -20643,7 +20643,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H83" s="13">
         <v>1</v>
@@ -20672,7 +20672,7 @@
         <v>21412</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C84" s="13">
         <v>10</v>
@@ -20687,7 +20687,7 @@
         <v>0.11109999999999999</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H84" s="13">
         <v>7</v>
@@ -20716,7 +20716,7 @@
         <v>14329</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C85" s="13">
         <v>6</v>
@@ -20731,7 +20731,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H85" s="13">
         <v>5</v>
@@ -20760,7 +20760,7 @@
         <v>23716</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C86" s="13">
         <v>7</v>
@@ -20775,7 +20775,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H86" s="13">
         <v>7</v>
@@ -20804,7 +20804,7 @@
         <v>24598</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C87" s="13">
         <v>17</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H87" s="13">
         <v>9</v>
@@ -20848,7 +20848,7 @@
         <v>19599</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C88" s="13">
         <v>26</v>
@@ -20863,7 +20863,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H88" s="13">
         <v>10</v>
@@ -20892,7 +20892,7 @@
         <v>19600</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C89" s="13">
         <v>16</v>
@@ -20936,7 +20936,7 @@
         <v>21432</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C90" s="13">
         <v>17</v>
@@ -20951,7 +20951,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H90" s="13">
         <v>19</v>
@@ -20980,7 +20980,7 @@
         <v>7430</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C91" s="13">
         <v>18</v>
@@ -20995,7 +20995,7 @@
         <v>0.1176</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H91" s="13">
         <v>9</v>
@@ -21024,7 +21024,7 @@
         <v>21363</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C92" s="13">
         <v>33</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H92" s="13">
         <v>18</v>
@@ -21068,7 +21068,7 @@
         <v>21765</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C93" s="13">
         <v>1</v>
@@ -21083,7 +21083,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H93" s="13">
         <v>1</v>
@@ -21112,7 +21112,7 @@
         <v>24584</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C94" s="13">
         <v>10</v>
@@ -21156,7 +21156,7 @@
         <v>21428</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C95" s="13">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H95" s="13">
         <v>21</v>
@@ -21200,7 +21200,7 @@
         <v>12175</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C96" s="13">
         <v>43</v>
@@ -21215,7 +21215,7 @@
         <v>0.030299999999999997</v>
       </c>
       <c r="G96" s="15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H96" s="13">
         <v>20</v>
@@ -21244,7 +21244,7 @@
         <v>21412</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C97" s="13">
         <v>5</v>
@@ -21259,7 +21259,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H97" s="13">
         <v>4</v>
@@ -21288,7 +21288,7 @@
         <v>23772</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C98" s="13">
         <v>10</v>
@@ -21303,7 +21303,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H98" s="13">
         <v>5</v>
@@ -21332,7 +21332,7 @@
         <v>20933</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C99" s="13">
         <v>10</v>
@@ -21347,7 +21347,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H99" s="13">
         <v>6</v>
@@ -21376,7 +21376,7 @@
         <v>11779</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C100" s="13">
         <v>14</v>
@@ -21391,7 +21391,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H100" s="13">
         <v>16</v>
@@ -21420,7 +21420,7 @@
         <v>23820</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C101" s="13">
         <v>6</v>
@@ -21435,7 +21435,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H101" s="13">
         <v>2</v>
@@ -21464,7 +21464,7 @@
         <v>21316</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C102" s="13">
         <v>11</v>
@@ -21508,7 +21508,7 @@
         <v>23473</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C103" s="13">
         <v>10</v>
@@ -21523,7 +21523,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H103" s="13">
         <v>10</v>
@@ -21552,7 +21552,7 @@
         <v>7423</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C104" s="13">
         <v>12</v>
@@ -21567,7 +21567,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H104" s="13">
         <v>9</v>
@@ -21596,7 +21596,7 @@
         <v>7430</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C105" s="13">
         <v>12</v>
@@ -21611,7 +21611,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H105" s="13">
         <v>7</v>
@@ -21640,7 +21640,7 @@
         <v>21750</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C106" s="13">
         <v>21</v>
@@ -21684,7 +21684,7 @@
         <v>20934</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C107" s="13">
         <v>18</v>
@@ -21699,7 +21699,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H107" s="13">
         <v>10</v>
@@ -21728,7 +21728,7 @@
         <v>21414</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C108" s="13">
         <v>4</v>
@@ -21743,7 +21743,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H108" s="13">
         <v>3</v>
@@ -21772,7 +21772,7 @@
         <v>24596</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C109" s="13">
         <v>19</v>
@@ -21787,7 +21787,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H109" s="13">
         <v>12</v>
@@ -21816,7 +21816,7 @@
         <v>21418</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C110" s="13">
         <v>0</v>
@@ -21831,7 +21831,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H110" s="13">
         <v>6</v>
@@ -21860,7 +21860,7 @@
         <v>12647</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C111" s="13">
         <v>35</v>
@@ -21904,7 +21904,7 @@
         <v>11591</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C112" s="13">
         <v>17</v>
@@ -21919,7 +21919,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H112" s="13">
         <v>14</v>
@@ -21948,7 +21948,7 @@
         <v>21376</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C113" s="13">
         <v>19</v>
@@ -21992,7 +21992,7 @@
         <v>21432</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C114" s="13">
         <v>18</v>
@@ -22007,7 +22007,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H114" s="13">
         <v>17</v>
@@ -22036,7 +22036,7 @@
         <v>7423</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C115" s="13">
         <v>13</v>
@@ -22051,7 +22051,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H115" s="13">
         <v>8</v>
@@ -22080,7 +22080,7 @@
         <v>23826</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C116" s="13">
         <v>6</v>
@@ -22095,7 +22095,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H116" s="13">
         <v>4</v>
@@ -22124,7 +22124,7 @@
         <v>21418</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C117" s="13">
         <v>29</v>
@@ -22139,7 +22139,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H117" s="13">
         <v>21</v>
@@ -22165,90 +22165,90 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="11">
-        <v>21764</v>
+        <v>21766</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C118" s="13">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D118" s="13">
         <v>0</v>
       </c>
       <c r="E118" s="14">
-        <v>4</v>
+        <v>0.7826000000000001</v>
       </c>
       <c r="F118" s="14">
         <v>0</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>329</v>
+        <v>516</v>
       </c>
       <c r="H118" s="13">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I118" s="13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J118" s="13">
         <v>0</v>
       </c>
       <c r="K118" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L118" s="14">
-        <v>0</v>
+        <v>0.6087</v>
       </c>
       <c r="M118" s="14">
         <v>0</v>
       </c>
       <c r="N118" s="14">
-        <v>0</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="11">
-        <v>21766</v>
+        <v>21764</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C119" s="13">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D119" s="13">
         <v>0</v>
       </c>
       <c r="E119" s="14">
-        <v>0.7826000000000001</v>
+        <v>4</v>
       </c>
       <c r="F119" s="14">
         <v>0</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>515</v>
+        <v>330</v>
       </c>
       <c r="H119" s="13">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I119" s="13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J119" s="13">
         <v>0</v>
       </c>
       <c r="K119" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L119" s="14">
-        <v>0.6087</v>
+        <v>0</v>
       </c>
       <c r="M119" s="14">
         <v>0</v>
       </c>
       <c r="N119" s="14">
-        <v>0.2143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -22256,7 +22256,7 @@
         <v>20933</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C120" s="13">
         <v>9</v>
@@ -22271,7 +22271,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H120" s="13">
         <v>6</v>
@@ -22300,7 +22300,7 @@
         <v>7427</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C121" s="13">
         <v>13</v>
@@ -22315,7 +22315,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H121" s="13">
         <v>11</v>
@@ -22344,7 +22344,7 @@
         <v>21750</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C122" s="13">
         <v>0</v>
@@ -22359,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H122" s="13">
         <v>1</v>
@@ -22388,7 +22388,7 @@
         <v>7432</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C123" s="13">
         <v>14</v>
@@ -22403,7 +22403,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H123" s="13">
         <v>7</v>
@@ -22432,7 +22432,7 @@
         <v>21430</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C124" s="13">
         <v>14</v>
@@ -22447,7 +22447,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H124" s="13">
         <v>12</v>
@@ -22476,7 +22476,7 @@
         <v>21113</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C125" s="13">
         <v>11</v>
@@ -22491,7 +22491,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H125" s="13">
         <v>8</v>
@@ -22520,7 +22520,7 @@
         <v>911955</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C126" s="13">
         <v>29</v>
@@ -22535,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H126" s="13">
         <v>28</v>
@@ -22564,7 +22564,7 @@
         <v>12175</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C127" s="13">
         <v>33</v>
@@ -22579,7 +22579,7 @@
         <v>0.0323</v>
       </c>
       <c r="G127" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H127" s="13">
         <v>18</v>
@@ -22608,7 +22608,7 @@
         <v>11992</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C128" s="13">
         <v>47</v>
@@ -22652,7 +22652,7 @@
         <v>19602</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C129" s="13">
         <v>12</v>
@@ -22667,7 +22667,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="15" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H129" s="13">
         <v>12</v>
@@ -22696,7 +22696,7 @@
         <v>21418</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C130" s="13">
         <v>16</v>
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H130" s="13">
         <v>15</v>
@@ -22740,7 +22740,7 @@
         <v>23775</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C131" s="13">
         <v>14</v>
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H131" s="13">
         <v>17</v>
@@ -22784,7 +22784,7 @@
         <v>7425</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C132" s="13">
         <v>28</v>
@@ -22799,7 +22799,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H132" s="13">
         <v>25</v>
@@ -22828,7 +22828,7 @@
         <v>24592</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C133" s="13">
         <v>17</v>
@@ -22872,7 +22872,7 @@
         <v>21428</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C134" s="13">
         <v>26</v>
@@ -22887,7 +22887,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H134" s="13">
         <v>18</v>
@@ -22916,7 +22916,7 @@
         <v>12647</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C135" s="13">
         <v>24</v>
@@ -22931,7 +22931,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H135" s="13">
         <v>13</v>
@@ -22960,7 +22960,7 @@
         <v>12517</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C136" s="13">
         <v>12</v>
@@ -22975,7 +22975,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H136" s="13">
         <v>10</v>
@@ -23004,7 +23004,7 @@
         <v>21418</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C137" s="13">
         <v>0</v>
@@ -23019,7 +23019,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H137" s="13">
         <v>1</v>
@@ -23048,7 +23048,7 @@
         <v>21415</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C138" s="13">
         <v>21</v>
@@ -23063,7 +23063,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H138" s="13">
         <v>17</v>
@@ -23092,7 +23092,7 @@
         <v>21762</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C139" s="13">
         <v>17</v>
@@ -23107,7 +23107,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H139" s="13">
         <v>15</v>
@@ -23136,7 +23136,7 @@
         <v>21419</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C140" s="13">
         <v>16</v>
@@ -23151,7 +23151,7 @@
         <v>0.0667</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H140" s="13">
         <v>13</v>
@@ -23180,7 +23180,7 @@
         <v>21363</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C141" s="13">
         <v>2</v>
@@ -23195,7 +23195,7 @@
         <v>0</v>
       </c>
       <c r="G141" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H141" s="13">
         <v>1</v>
@@ -23224,7 +23224,7 @@
         <v>21432</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C142" s="13">
         <v>6</v>
@@ -23239,7 +23239,7 @@
         <v>0</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H142" s="13">
         <v>4</v>
@@ -23268,7 +23268,7 @@
         <v>23826</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C143" s="13">
         <v>6</v>
@@ -23283,7 +23283,7 @@
         <v>0</v>
       </c>
       <c r="G143" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H143" s="13">
         <v>5</v>
@@ -23312,7 +23312,7 @@
         <v>24584</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C144" s="13">
         <v>27</v>
@@ -23327,7 +23327,7 @@
         <v>0</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H144" s="13">
         <v>22</v>
@@ -23356,7 +23356,7 @@
         <v>20931</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C145" s="13">
         <v>15</v>
@@ -23371,7 +23371,7 @@
         <v>0</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H145" s="13">
         <v>10</v>
@@ -23400,7 +23400,7 @@
         <v>21419</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C146" s="13">
         <v>18</v>
@@ -23415,7 +23415,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H146" s="13">
         <v>19</v>
@@ -23444,7 +23444,7 @@
         <v>21421</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C147" s="13">
         <v>22</v>
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H147" s="13">
         <v>22</v>
@@ -23488,7 +23488,7 @@
         <v>13214</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C148" s="13">
         <v>3</v>
@@ -23503,7 +23503,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H148" s="13">
         <v>0</v>
@@ -23532,7 +23532,7 @@
         <v>21418</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C149" s="13">
         <v>23</v>
@@ -23547,7 +23547,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H149" s="13">
         <v>23</v>
@@ -23576,7 +23576,7 @@
         <v>21429</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C150" s="13">
         <v>12</v>
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H150" s="13">
         <v>13</v>
@@ -23620,7 +23620,7 @@
         <v>24585</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C151" s="13">
         <v>14</v>
@@ -23635,7 +23635,7 @@
         <v>0</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H151" s="13">
         <v>8</v>
@@ -23664,7 +23664,7 @@
         <v>23778</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C152" s="13">
         <v>6</v>
@@ -23708,7 +23708,7 @@
         <v>7432</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C153" s="13">
         <v>20</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H153" s="13">
         <v>13</v>
@@ -23752,7 +23752,7 @@
         <v>21424</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C154" s="13">
         <v>14</v>
@@ -23767,7 +23767,7 @@
         <v>0</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H154" s="13">
         <v>13</v>
@@ -23796,7 +23796,7 @@
         <v>20925</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C155" s="13">
         <v>13</v>
@@ -23840,7 +23840,7 @@
         <v>21418</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C156" s="13">
         <v>0</v>
@@ -23855,7 +23855,7 @@
         <v>0</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H156" s="13">
         <v>1</v>
@@ -23884,7 +23884,7 @@
         <v>24597</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C157" s="13">
         <v>11</v>
@@ -23899,7 +23899,7 @@
         <v>0</v>
       </c>
       <c r="G157" s="15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H157" s="13">
         <v>6</v>
@@ -23928,7 +23928,7 @@
         <v>21561</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C158" s="13">
         <v>23</v>
@@ -23943,7 +23943,7 @@
         <v>0</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H158" s="13">
         <v>7</v>
@@ -23972,7 +23972,7 @@
         <v>21429</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C159" s="13">
         <v>16</v>
@@ -23987,7 +23987,7 @@
         <v>0</v>
       </c>
       <c r="G159" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H159" s="13">
         <v>14</v>
@@ -24016,7 +24016,7 @@
         <v>11983</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C160" s="13">
         <v>22</v>
@@ -24031,7 +24031,7 @@
         <v>0</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H160" s="13">
         <v>16</v>
@@ -24060,7 +24060,7 @@
         <v>13214</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C161" s="13">
         <v>17</v>
@@ -24075,7 +24075,7 @@
         <v>0</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H161" s="13">
         <v>15</v>
@@ -24104,7 +24104,7 @@
         <v>21763</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C162" s="13">
         <v>11</v>
@@ -24148,7 +24148,7 @@
         <v>7432</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C163" s="13">
         <v>28</v>
@@ -24163,7 +24163,7 @@
         <v>0</v>
       </c>
       <c r="G163" s="15" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H163" s="13">
         <v>15</v>
@@ -24192,7 +24192,7 @@
         <v>24596</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C164" s="13">
         <v>7</v>
@@ -24236,7 +24236,7 @@
         <v>11779</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C165" s="13">
         <v>20</v>
@@ -24251,7 +24251,7 @@
         <v>0</v>
       </c>
       <c r="G165" s="15" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H165" s="13">
         <v>15</v>
@@ -24280,7 +24280,7 @@
         <v>24597</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C166" s="13">
         <v>15</v>
@@ -24295,7 +24295,7 @@
         <v>0</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H166" s="13">
         <v>6</v>
@@ -24324,7 +24324,7 @@
         <v>911955</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C167" s="13">
         <v>5</v>
@@ -24339,7 +24339,7 @@
         <v>0</v>
       </c>
       <c r="G167" s="15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H167" s="13">
         <v>3</v>
@@ -24368,7 +24368,7 @@
         <v>21113</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C168" s="13">
         <v>7</v>
@@ -24383,7 +24383,7 @@
         <v>0</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H168" s="13">
         <v>8</v>
@@ -24412,7 +24412,7 @@
         <v>911770</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C169" s="13">
         <v>16</v>
@@ -24456,7 +24456,7 @@
         <v>21413</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C170" s="13">
         <v>21</v>
@@ -24500,7 +24500,7 @@
         <v>21026</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C171" s="13">
         <v>3</v>
@@ -24515,7 +24515,7 @@
         <v>0</v>
       </c>
       <c r="G171" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H171" s="13">
         <v>3</v>
@@ -24544,7 +24544,7 @@
         <v>11591</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C172" s="13">
         <v>17</v>
@@ -24559,7 +24559,7 @@
         <v>0</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H172" s="13">
         <v>12</v>
@@ -24588,7 +24588,7 @@
         <v>21418</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C173" s="13">
         <v>21</v>
@@ -24603,7 +24603,7 @@
         <v>0</v>
       </c>
       <c r="G173" s="15" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H173" s="13">
         <v>21</v>
@@ -24632,7 +24632,7 @@
         <v>7431</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C174" s="13">
         <v>13</v>
@@ -24676,7 +24676,7 @@
         <v>911770</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C175" s="13">
         <v>9</v>
@@ -24691,7 +24691,7 @@
         <v>0</v>
       </c>
       <c r="G175" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H175" s="13">
         <v>9</v>
@@ -24720,7 +24720,7 @@
         <v>21419</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C176" s="13">
         <v>22</v>
@@ -24735,7 +24735,7 @@
         <v>0</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H176" s="13">
         <v>15</v>
@@ -24764,7 +24764,7 @@
         <v>23776</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C177" s="13">
         <v>7</v>
@@ -24779,7 +24779,7 @@
         <v>0</v>
       </c>
       <c r="G177" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H177" s="13">
         <v>2</v>
@@ -24808,7 +24808,7 @@
         <v>21750</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C178" s="13">
         <v>21</v>
@@ -24823,7 +24823,7 @@
         <v>0</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H178" s="13">
         <v>18</v>
@@ -24852,7 +24852,7 @@
         <v>21122</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C179" s="13">
         <v>15</v>
@@ -24867,7 +24867,7 @@
         <v>0</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H179" s="13">
         <v>11</v>
@@ -24896,7 +24896,7 @@
         <v>11779</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C180" s="13">
         <v>22</v>
@@ -24911,7 +24911,7 @@
         <v>0</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H180" s="13">
         <v>13</v>
@@ -24940,7 +24940,7 @@
         <v>20856</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C181" s="13">
         <v>17</v>
@@ -24955,7 +24955,7 @@
         <v>0</v>
       </c>
       <c r="G181" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H181" s="13">
         <v>13</v>
@@ -24984,7 +24984,7 @@
         <v>21113</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C182" s="13">
         <v>10</v>
@@ -25028,7 +25028,7 @@
         <v>21418</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C183" s="13">
         <v>22</v>
@@ -25072,7 +25072,7 @@
         <v>20934</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C184" s="13">
         <v>31</v>
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H184" s="13">
         <v>15</v>
@@ -25116,7 +25116,7 @@
         <v>11582</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C185" s="13">
         <v>21</v>
@@ -25160,7 +25160,7 @@
         <v>14045</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C186" s="13">
         <v>13</v>
@@ -25204,7 +25204,7 @@
         <v>20934</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C187" s="13">
         <v>32</v>
@@ -25219,7 +25219,7 @@
         <v>0.035699999999999996</v>
       </c>
       <c r="G187" s="15" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H187" s="13">
         <v>17</v>
@@ -25248,7 +25248,7 @@
         <v>21560</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C188" s="13">
         <v>4</v>
@@ -25263,7 +25263,7 @@
         <v>0</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H188" s="13">
         <v>3</v>
@@ -25292,7 +25292,7 @@
         <v>21761</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C189" s="13">
         <v>7</v>
@@ -25336,7 +25336,7 @@
         <v>12643</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C190" s="13">
         <v>36</v>
@@ -25351,7 +25351,7 @@
         <v>0</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H190" s="13">
         <v>26</v>
@@ -25377,31 +25377,31 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="11">
-        <v>23775</v>
+        <v>23774</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C191" s="13">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D191" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E191" s="14">
-        <v>4</v>
+        <v>1.0714</v>
       </c>
       <c r="F191" s="14">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="G191" s="15" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
       <c r="H191" s="13">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I191" s="13">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J191" s="13">
         <v>0</v>
@@ -25421,31 +25421,31 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="11">
-        <v>23774</v>
+        <v>23775</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C192" s="13">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D192" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E192" s="14">
-        <v>1.0714</v>
+        <v>4</v>
       </c>
       <c r="F192" s="14">
-        <v>0.1176</v>
+        <v>0</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>304</v>
+        <v>234</v>
       </c>
       <c r="H192" s="13">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I192" s="13">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J192" s="13">
         <v>0</v>
@@ -25468,7 +25468,7 @@
         <v>24805</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C193" s="13">
         <v>3</v>
@@ -25483,7 +25483,7 @@
         <v>0.3333</v>
       </c>
       <c r="G193" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H193" s="13">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>21560</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C194" s="13">
         <v>5</v>
@@ -25527,7 +25527,7 @@
         <v>0</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H194" s="13">
         <v>5</v>
@@ -25553,31 +25553,31 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="11">
-        <v>23778</v>
+        <v>23773</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C195" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D195" s="13">
         <v>0</v>
       </c>
       <c r="E195" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F195" s="14">
         <v>0</v>
       </c>
       <c r="G195" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H195" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I195" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J195" s="13">
         <v>0</v>
@@ -25597,31 +25597,31 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="11">
-        <v>23773</v>
+        <v>23778</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C196" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D196" s="13">
         <v>0</v>
       </c>
       <c r="E196" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F196" s="14">
         <v>0</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H196" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I196" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J196" s="13">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>21561</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C197" s="13">
         <v>25</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="G197" s="15" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H197" s="13">
         <v>9</v>
@@ -25688,7 +25688,7 @@
         <v>19603</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C198" s="13">
         <v>11</v>
@@ -25703,7 +25703,7 @@
         <v>0</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H198" s="13">
         <v>11</v>
@@ -25732,7 +25732,7 @@
         <v>11983</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C199" s="13">
         <v>10</v>
@@ -25776,7 +25776,7 @@
         <v>24593</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C200" s="13">
         <v>2</v>
@@ -25791,7 +25791,7 @@
         <v>0</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H200" s="13">
         <v>3</v>
@@ -25820,7 +25820,7 @@
         <v>24595</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C201" s="13">
         <v>14</v>
@@ -25864,7 +25864,7 @@
         <v>21432</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C202" s="13">
         <v>10</v>
@@ -25879,7 +25879,7 @@
         <v>0</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H202" s="13">
         <v>11</v>
@@ -25908,7 +25908,7 @@
         <v>21421</v>
       </c>
       <c r="B203" s="12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C203" s="13">
         <v>23</v>
@@ -25923,7 +25923,7 @@
         <v>0</v>
       </c>
       <c r="G203" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H203" s="13">
         <v>10</v>
@@ -25952,7 +25952,7 @@
         <v>24585</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C204" s="13">
         <v>29</v>
@@ -25967,7 +25967,7 @@
         <v>0.069</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H204" s="13">
         <v>11</v>
@@ -25996,7 +25996,7 @@
         <v>19603</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C205" s="13">
         <v>10</v>
@@ -26011,7 +26011,7 @@
         <v>0</v>
       </c>
       <c r="G205" s="15" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H205" s="13">
         <v>7</v>
@@ -26040,7 +26040,7 @@
         <v>24592</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C206" s="13">
         <v>9</v>
@@ -26055,7 +26055,7 @@
         <v>0</v>
       </c>
       <c r="G206" s="15" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H206" s="13">
         <v>7</v>
@@ -26084,7 +26084,7 @@
         <v>21414</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C207" s="13">
         <v>3</v>
@@ -26099,7 +26099,7 @@
         <v>0</v>
       </c>
       <c r="G207" s="15" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H207" s="13">
         <v>3</v>
@@ -26128,7 +26128,7 @@
         <v>24599</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C208" s="13">
         <v>0</v>
@@ -26143,7 +26143,7 @@
         <v>0</v>
       </c>
       <c r="G208" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H208" s="13">
         <v>7</v>
@@ -26172,7 +26172,7 @@
         <v>24593</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C209" s="13">
         <v>4</v>
@@ -26187,7 +26187,7 @@
         <v>0</v>
       </c>
       <c r="G209" s="15" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H209" s="13">
         <v>3</v>
@@ -26216,7 +26216,7 @@
         <v>19595</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C210" s="13">
         <v>18</v>
@@ -26231,7 +26231,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H210" s="13">
         <v>16</v>
@@ -26260,7 +26260,7 @@
         <v>12647</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C211" s="13">
         <v>18</v>
@@ -26275,7 +26275,7 @@
         <v>0</v>
       </c>
       <c r="G211" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H211" s="13">
         <v>13</v>
@@ -26304,7 +26304,7 @@
         <v>24598</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C212" s="13">
         <v>10</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H212" s="13">
         <v>6</v>
@@ -26348,7 +26348,7 @@
         <v>7424</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C213" s="13">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>0</v>
       </c>
       <c r="G213" s="15" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H213" s="13">
         <v>9</v>
@@ -26392,7 +26392,7 @@
         <v>21766</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C214" s="13">
         <v>22</v>
@@ -26436,7 +26436,7 @@
         <v>21026</v>
       </c>
       <c r="B215" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C215" s="13">
         <v>15</v>
@@ -26451,7 +26451,7 @@
         <v>0</v>
       </c>
       <c r="G215" s="15" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H215" s="13">
         <v>14</v>
@@ -26480,7 +26480,7 @@
         <v>21413</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C216" s="13">
         <v>20</v>
@@ -26495,7 +26495,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H216" s="13">
         <v>16</v>
@@ -26524,7 +26524,7 @@
         <v>21416</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C217" s="13">
         <v>21</v>
@@ -26539,7 +26539,7 @@
         <v>0</v>
       </c>
       <c r="G217" s="15" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H217" s="13">
         <v>14</v>
@@ -26568,7 +26568,7 @@
         <v>24805</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C218" s="13">
         <v>7</v>
@@ -26583,7 +26583,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H218" s="13">
         <v>4</v>
@@ -26612,7 +26612,7 @@
         <v>21431</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C219" s="13">
         <v>17</v>
@@ -26627,7 +26627,7 @@
         <v>0</v>
       </c>
       <c r="G219" s="15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H219" s="13">
         <v>12</v>
@@ -26656,7 +26656,7 @@
         <v>21418</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C220" s="13">
         <v>25</v>
@@ -26671,7 +26671,7 @@
         <v>0</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H220" s="13">
         <v>20</v>
@@ -26700,7 +26700,7 @@
         <v>21427</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C221" s="13">
         <v>25</v>
@@ -26715,7 +26715,7 @@
         <v>0.04</v>
       </c>
       <c r="G221" s="15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H221" s="13">
         <v>14</v>
@@ -26744,7 +26744,7 @@
         <v>21561</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C222" s="13">
         <v>39</v>
@@ -26759,7 +26759,7 @@
         <v>0</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H222" s="13">
         <v>11</v>
@@ -26788,7 +26788,7 @@
         <v>21363</v>
       </c>
       <c r="B223" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C223" s="13">
         <v>29</v>
@@ -26803,7 +26803,7 @@
         <v>0</v>
       </c>
       <c r="G223" s="15" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H223" s="13">
         <v>19</v>
@@ -26832,7 +26832,7 @@
         <v>11591</v>
       </c>
       <c r="B224" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C224" s="13">
         <v>18</v>
@@ -26847,7 +26847,7 @@
         <v>0</v>
       </c>
       <c r="G224" s="15" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H224" s="13">
         <v>9</v>
@@ -26876,7 +26876,7 @@
         <v>21421</v>
       </c>
       <c r="B225" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C225" s="13">
         <v>45</v>
@@ -26920,7 +26920,7 @@
         <v>21431</v>
       </c>
       <c r="B226" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C226" s="13">
         <v>21</v>
@@ -26964,7 +26964,7 @@
         <v>23772</v>
       </c>
       <c r="B227" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C227" s="13">
         <v>9</v>
@@ -26979,7 +26979,7 @@
         <v>0</v>
       </c>
       <c r="G227" s="15" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H227" s="13">
         <v>6</v>
@@ -27008,7 +27008,7 @@
         <v>7430</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C228" s="13">
         <v>4</v>
@@ -27023,7 +27023,7 @@
         <v>0</v>
       </c>
       <c r="G228" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H228" s="13">
         <v>5</v>
@@ -27052,7 +27052,7 @@
         <v>21418</v>
       </c>
       <c r="B229" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C229" s="13">
         <v>15</v>
@@ -27067,7 +27067,7 @@
         <v>0</v>
       </c>
       <c r="G229" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H229" s="13">
         <v>16</v>
@@ -27096,7 +27096,7 @@
         <v>21764</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C230" s="13">
         <v>18</v>
@@ -27111,7 +27111,7 @@
         <v>0</v>
       </c>
       <c r="G230" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H230" s="13">
         <v>16</v>
@@ -27140,7 +27140,7 @@
         <v>21421</v>
       </c>
       <c r="B231" s="12" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C231" s="13">
         <v>31</v>
@@ -27155,7 +27155,7 @@
         <v>0.0323</v>
       </c>
       <c r="G231" s="15" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H231" s="13">
         <v>16</v>
@@ -27184,7 +27184,7 @@
         <v>24599</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C232" s="13">
         <v>20</v>
@@ -27199,7 +27199,7 @@
         <v>0</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H232" s="13">
         <v>11</v>
@@ -27228,7 +27228,7 @@
         <v>21416</v>
       </c>
       <c r="B233" s="12" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C233" s="13">
         <v>1</v>
@@ -27243,7 +27243,7 @@
         <v>0</v>
       </c>
       <c r="G233" s="15" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H233" s="13">
         <v>0</v>
@@ -27272,7 +27272,7 @@
         <v>911770</v>
       </c>
       <c r="B234" s="12" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C234" s="13">
         <v>24</v>
@@ -27287,7 +27287,7 @@
         <v>0.16670000000000001</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H234" s="13">
         <v>9</v>
@@ -27316,7 +27316,7 @@
         <v>7423</v>
       </c>
       <c r="B235" s="12" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C235" s="13">
         <v>11</v>
@@ -27331,7 +27331,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H235" s="13">
         <v>7</v>
@@ -27360,7 +27360,7 @@
         <v>21424</v>
       </c>
       <c r="B236" s="12" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C236" s="13">
         <v>18</v>
@@ -27404,7 +27404,7 @@
         <v>23716</v>
       </c>
       <c r="B237" s="12" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C237" s="13">
         <v>10</v>
@@ -27419,7 +27419,7 @@
         <v>0</v>
       </c>
       <c r="G237" s="15" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H237" s="13">
         <v>8</v>
@@ -27448,7 +27448,7 @@
         <v>21418</v>
       </c>
       <c r="B238" s="12" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C238" s="13">
         <v>0</v>
@@ -27463,7 +27463,7 @@
         <v>0</v>
       </c>
       <c r="G238" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H238" s="13">
         <v>8</v>
@@ -27492,7 +27492,7 @@
         <v>19601</v>
       </c>
       <c r="B239" s="12" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C239" s="13">
         <v>3</v>
@@ -27507,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="G239" s="15" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H239" s="13">
         <v>3</v>
@@ -27536,7 +27536,7 @@
         <v>24594</v>
       </c>
       <c r="B240" s="12" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C240" s="13">
         <v>15</v>
@@ -27551,7 +27551,7 @@
         <v>0</v>
       </c>
       <c r="G240" s="15" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H240" s="13">
         <v>12</v>
@@ -27580,7 +27580,7 @@
         <v>23474</v>
       </c>
       <c r="B241" s="12" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C241" s="13">
         <v>13</v>
@@ -27595,7 +27595,7 @@
         <v>0</v>
       </c>
       <c r="G241" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H241" s="13">
         <v>11</v>
@@ -27624,7 +27624,7 @@
         <v>20763</v>
       </c>
       <c r="B242" s="12" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C242" s="13">
         <v>9</v>
@@ -27639,7 +27639,7 @@
         <v>0</v>
       </c>
       <c r="G242" s="15" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H242" s="13">
         <v>6</v>
@@ -27668,7 +27668,7 @@
         <v>11779</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C243" s="13">
         <v>15</v>
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="G243" s="15" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H243" s="13">
         <v>12</v>
@@ -27712,7 +27712,7 @@
         <v>19595</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C244" s="13">
         <v>11</v>
@@ -27756,7 +27756,7 @@
         <v>21764</v>
       </c>
       <c r="B245" s="12" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C245" s="13">
         <v>4</v>
@@ -27771,7 +27771,7 @@
         <v>0</v>
       </c>
       <c r="G245" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H245" s="13">
         <v>1</v>
@@ -27800,7 +27800,7 @@
         <v>21766</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C246" s="13">
         <v>21</v>
@@ -27815,7 +27815,7 @@
         <v>0</v>
       </c>
       <c r="G246" s="15" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H246" s="13">
         <v>21</v>
@@ -27844,7 +27844,7 @@
         <v>21419</v>
       </c>
       <c r="B247" s="12" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C247" s="13">
         <v>16</v>
@@ -27888,7 +27888,7 @@
         <v>21765</v>
       </c>
       <c r="B248" s="12" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C248" s="13">
         <v>17</v>
@@ -27903,7 +27903,7 @@
         <v>0</v>
       </c>
       <c r="G248" s="15" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H248" s="13">
         <v>15</v>
@@ -27932,7 +27932,7 @@
         <v>23717</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C249" s="13">
         <v>16</v>
@@ -27947,7 +27947,7 @@
         <v>0</v>
       </c>
       <c r="G249" s="15" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H249" s="13">
         <v>11</v>
@@ -27976,7 +27976,7 @@
         <v>21419</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C250" s="13">
         <v>14</v>
@@ -28020,7 +28020,7 @@
         <v>22054</v>
       </c>
       <c r="B251" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C251" s="13">
         <v>11</v>
@@ -28035,7 +28035,7 @@
         <v>0</v>
       </c>
       <c r="G251" s="15" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H251" s="13">
         <v>10</v>
@@ -28064,7 +28064,7 @@
         <v>20922</v>
       </c>
       <c r="B252" s="12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C252" s="13">
         <v>23</v>
@@ -28108,7 +28108,7 @@
         <v>12647</v>
       </c>
       <c r="B253" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C253" s="13">
         <v>17</v>
@@ -28123,7 +28123,7 @@
         <v>0</v>
       </c>
       <c r="G253" s="15" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H253" s="13">
         <v>15</v>
@@ -28152,7 +28152,7 @@
         <v>21365</v>
       </c>
       <c r="B254" s="12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C254" s="13">
         <v>25</v>
@@ -28167,7 +28167,7 @@
         <v>0</v>
       </c>
       <c r="G254" s="15" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H254" s="13">
         <v>11</v>
@@ -28196,7 +28196,7 @@
         <v>21411</v>
       </c>
       <c r="B255" s="12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C255" s="13">
         <v>13</v>
@@ -28211,7 +28211,7 @@
         <v>0</v>
       </c>
       <c r="G255" s="15" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H255" s="13">
         <v>11</v>
@@ -28240,7 +28240,7 @@
         <v>21762</v>
       </c>
       <c r="B256" s="12" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C256" s="13">
         <v>17</v>
@@ -28255,7 +28255,7 @@
         <v>0</v>
       </c>
       <c r="G256" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H256" s="13">
         <v>20</v>
@@ -28284,7 +28284,7 @@
         <v>14329</v>
       </c>
       <c r="B257" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C257" s="13">
         <v>11</v>
@@ -28299,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="G257" s="15" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H257" s="13">
         <v>11</v>
@@ -28328,7 +28328,7 @@
         <v>24597</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C258" s="13">
         <v>9</v>
@@ -28343,7 +28343,7 @@
         <v>0.125</v>
       </c>
       <c r="G258" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H258" s="13">
         <v>7</v>
@@ -28372,7 +28372,7 @@
         <v>21764</v>
       </c>
       <c r="B259" s="12" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C259" s="13">
         <v>5</v>
@@ -28387,7 +28387,7 @@
         <v>0</v>
       </c>
       <c r="G259" s="15" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H259" s="13">
         <v>11</v>
@@ -28416,7 +28416,7 @@
         <v>12647</v>
       </c>
       <c r="B260" s="12" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C260" s="13">
         <v>31</v>
@@ -28460,7 +28460,7 @@
         <v>24598</v>
       </c>
       <c r="B261" s="12" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C261" s="13">
         <v>11</v>
@@ -28475,7 +28475,7 @@
         <v>0</v>
       </c>
       <c r="G261" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H261" s="13">
         <v>11</v>
@@ -28504,7 +28504,7 @@
         <v>23768</v>
       </c>
       <c r="B262" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C262" s="13">
         <v>8</v>
@@ -28519,7 +28519,7 @@
         <v>0</v>
       </c>
       <c r="G262" s="15" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H262" s="13">
         <v>7</v>
@@ -28548,7 +28548,7 @@
         <v>7423</v>
       </c>
       <c r="B263" s="12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C263" s="13">
         <v>11</v>
@@ -28563,7 +28563,7 @@
         <v>0</v>
       </c>
       <c r="G263" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H263" s="13">
         <v>11</v>
@@ -28592,7 +28592,7 @@
         <v>21421</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C264" s="13">
         <v>26</v>
@@ -28636,7 +28636,7 @@
         <v>23474</v>
       </c>
       <c r="B265" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C265" s="13">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>0</v>
       </c>
       <c r="G265" s="15" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H265" s="13">
         <v>8</v>
@@ -28680,7 +28680,7 @@
         <v>20934</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C266" s="13">
         <v>20</v>
@@ -28724,7 +28724,7 @@
         <v>21364</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C267" s="13">
         <v>20</v>
@@ -28739,7 +28739,7 @@
         <v>0</v>
       </c>
       <c r="G267" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H267" s="13">
         <v>21</v>
@@ -28768,7 +28768,7 @@
         <v>21750</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C268" s="13">
         <v>22</v>
@@ -28783,7 +28783,7 @@
         <v>0</v>
       </c>
       <c r="G268" s="15" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H268" s="13">
         <v>23</v>
@@ -28812,7 +28812,7 @@
         <v>11992</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C269" s="13">
         <v>23</v>
@@ -28827,7 +28827,7 @@
         <v>0</v>
       </c>
       <c r="G269" s="15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H269" s="13">
         <v>17</v>
@@ -28856,7 +28856,7 @@
         <v>23773</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C270" s="13">
         <v>13</v>
@@ -28900,7 +28900,7 @@
         <v>22054</v>
       </c>
       <c r="B271" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C271" s="13">
         <v>12</v>
@@ -28944,7 +28944,7 @@
         <v>24595</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C272" s="13">
         <v>10</v>
@@ -28959,7 +28959,7 @@
         <v>0</v>
       </c>
       <c r="G272" s="15" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H272" s="13">
         <v>6</v>
@@ -28985,31 +28985,31 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="11">
-        <v>21761</v>
+        <v>21765</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C273" s="13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D273" s="13">
         <v>0</v>
       </c>
       <c r="E273" s="14">
-        <v>3.3333</v>
+        <v>7</v>
       </c>
       <c r="F273" s="14">
         <v>0</v>
       </c>
       <c r="G273" s="15" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H273" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I273" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J273" s="13">
         <v>0</v>
@@ -29029,31 +29029,31 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" s="11">
-        <v>21765</v>
+        <v>21761</v>
       </c>
       <c r="B274" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C274" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D274" s="13">
         <v>0</v>
       </c>
       <c r="E274" s="14">
-        <v>7</v>
+        <v>3.3333</v>
       </c>
       <c r="F274" s="14">
         <v>0</v>
       </c>
       <c r="G274" s="15" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H274" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I274" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J274" s="13">
         <v>0</v>
@@ -29076,7 +29076,7 @@
         <v>11992</v>
       </c>
       <c r="B275" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C275" s="13">
         <v>23</v>
@@ -29091,7 +29091,7 @@
         <v>0</v>
       </c>
       <c r="G275" s="15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H275" s="13">
         <v>19</v>
@@ -29120,7 +29120,7 @@
         <v>22054</v>
       </c>
       <c r="B276" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C276" s="13">
         <v>8</v>
@@ -29135,7 +29135,7 @@
         <v>0</v>
       </c>
       <c r="G276" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H276" s="13">
         <v>5</v>
@@ -29164,7 +29164,7 @@
         <v>12175</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C277" s="13">
         <v>26</v>
@@ -29179,7 +29179,7 @@
         <v>0.0435</v>
       </c>
       <c r="G277" s="15" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H277" s="13">
         <v>14</v>
@@ -29208,7 +29208,7 @@
         <v>21122</v>
       </c>
       <c r="B278" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C278" s="13">
         <v>18</v>
@@ -29252,7 +29252,7 @@
         <v>12488</v>
       </c>
       <c r="B279" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C279" s="13">
         <v>22</v>
@@ -29296,7 +29296,7 @@
         <v>21113</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C280" s="13">
         <v>7</v>
@@ -29311,7 +29311,7 @@
         <v>0</v>
       </c>
       <c r="G280" s="15" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H280" s="13">
         <v>6</v>
@@ -29340,7 +29340,7 @@
         <v>24599</v>
       </c>
       <c r="B281" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C281" s="13">
         <v>10</v>
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="G281" s="15" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H281" s="13">
         <v>9</v>
@@ -29384,7 +29384,7 @@
         <v>21765</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C282" s="13">
         <v>13</v>
@@ -29399,7 +29399,7 @@
         <v>0</v>
       </c>
       <c r="G282" s="15" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H282" s="13">
         <v>18</v>
@@ -29428,7 +29428,7 @@
         <v>7424</v>
       </c>
       <c r="B283" s="12" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C283" s="13">
         <v>11</v>
@@ -29443,7 +29443,7 @@
         <v>0</v>
       </c>
       <c r="G283" s="15" t="s">
-        <v>756</v>
+        <v>416</v>
       </c>
       <c r="H283" s="13">
         <v>9</v>
@@ -29575,7 +29575,7 @@
         <v>0</v>
       </c>
       <c r="G286" s="15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H286" s="13">
         <v>12</v>
@@ -29619,7 +29619,7 @@
         <v>0</v>
       </c>
       <c r="G287" s="15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H287" s="13">
         <v>17</v>
@@ -29663,7 +29663,7 @@
         <v>0</v>
       </c>
       <c r="G288" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H288" s="13">
         <v>37</v>
@@ -29751,7 +29751,7 @@
         <v>0</v>
       </c>
       <c r="G290" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H290" s="13">
         <v>13</v>
@@ -30323,7 +30323,7 @@
         <v>0</v>
       </c>
       <c r="G303" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H303" s="13">
         <v>20</v>
@@ -30367,7 +30367,7 @@
         <v>0</v>
       </c>
       <c r="G304" s="15" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H304" s="13">
         <v>3</v>
@@ -30455,7 +30455,7 @@
         <v>0</v>
       </c>
       <c r="G306" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H306" s="13">
         <v>1</v>
@@ -30499,7 +30499,7 @@
         <v>0</v>
       </c>
       <c r="G307" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H307" s="13">
         <v>1</v>
@@ -30527,315 +30527,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D234EE65F395364381EDD56E2B2CEC2E" ma:contentTypeVersion="22" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="239b82439aa111ba5f541e0caa94f1c1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57102c03-d0e5-4eb3-b845-71677c5a2af8" xmlns:ns3="11650913-886e-4af1-8fb4-e96f880a527d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87cc35a412700c5356edadb0dae0cc87" ns2:_="" ns3:_="">
-    <xsd:import namespace="57102c03-d0e5-4eb3-b845-71677c5a2af8"/>
-    <xsd:import namespace="11650913-886e-4af1-8fb4-e96f880a527d"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:a656750765d84742b9564d5f2541635c" minOccurs="0"/>
-                <xsd:element ref="ns2:_x0030_1" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="57102c03-d0e5-4eb3-b845-71677c5a2af8" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f98cd274-88c9-4048-a4aa-c02285319f4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="a656750765d84742b9564d5f2541635c" ma:index="28" nillable="true" ma:taxonomy="true" ma:internalName="a656750765d84742b9564d5f2541635c" ma:taxonomyFieldName="data" ma:displayName="data" ma:default="" ma:fieldId="{a6567507-65d8-4742-b956-4d5f2541635c}" ma:sspId="f98cd274-88c9-4048-a4aa-c02285319f4f" ma:termSetId="386095d1-c68d-4c6d-b587-48ddaf1aecc9" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="_x0030_1" ma:index="29" nillable="true" ma:displayName="01" ma:format="Dropdown" ma:internalName="_x0030_1" ma:percentage="FALSE">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Number"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="11650913-886e-4af1-8fb4-e96f880a527d" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{9bdceb6f-c556-4f78-9ca5-8766f0eea969}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="11650913-886e-4af1-8fb4-e96f880a527d">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57102c03-d0e5-4eb3-b845-71677c5a2af8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <a656750765d84742b9564d5f2541635c xmlns="57102c03-d0e5-4eb3-b845-71677c5a2af8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </a656750765d84742b9564d5f2541635c>
-    <TaxCatchAll xmlns="11650913-886e-4af1-8fb4-e96f880a527d" xsi:nil="true"/>
-    <_x0030_1 xmlns="57102c03-d0e5-4eb3-b845-71677c5a2af8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B53C40CD-212B-4DC7-B254-403A24A740E8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F214A3B-8CDA-431D-A538-2EE2582979E1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90DA763B-8DAA-441F-A9E4-5F97282BDE2D}"/>
 </file>